--- a/assets/constructions/examples/ctd_die_f1.xlsx
+++ b/assets/constructions/examples/ctd_die_f1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,11 +584,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TDM085R5SCF12M</t>
+          <t>TDM140R8SCF16M</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -603,12 +623,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>WID_TopDrill_W11</t>
+          <t>WID_TopDrill_W22</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -617,13 +637,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8.5</v>
+        <v>14</v>
       </c>
       <c r="H2" t="n">
-        <v>8.99</v>
+        <v>14.49</v>
       </c>
       <c r="I2" t="n">
-        <v>8.5</v>
+        <v>14</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -642,19 +662,19 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>45</v>
+        <v>116</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.006</v>
+        <v>8.006</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>ISO_9766:12</t>
+          <t>ISO_9766:16</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>WIDIA_TopDrill_W11</t>
+          <t>WIDIA_TopDrill_W22</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -665,19 +685,19 @@
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="X2" t="n">
-        <v>106.5</v>
+        <v>188</v>
       </c>
       <c r="Y2" t="n">
-        <v>61.5</v>
+        <v>140</v>
       </c>
       <c r="Z2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AA2" t="n">
-        <v>56</v>
+        <v>134.5</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
@@ -689,11 +709,17 @@
           <t>2017 / Widia Master Catalogue RU</t>
         </is>
       </c>
+      <c r="AF2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TDM210R5SCF25M</t>
+          <t>TDMX260R3SL32M</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,17 +729,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TOP DRILL M1</t>
+          <t>Top Drill Modular X</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>W30</t>
+          <t>K</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>WID_TopDrill_W30</t>
+          <t>WID_TopDrillX_K</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -722,17 +748,17 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H3" t="n">
-        <v>21.99</v>
+        <v>26.999</v>
       </c>
       <c r="I3" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>TDM..</t>
+          <t>TDMX..</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -747,19 +773,19 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.002</v>
+        <v>3</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>ISO_9766:25</t>
+          <t>ISO_9766:32</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>WIDIA_TopDrill_W30</t>
+          <t>WIDIA_TopDrillX_K</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -770,20 +796,18 @@
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="X3" t="n">
-        <v>199.5</v>
+        <v>186</v>
       </c>
       <c r="Y3" t="n">
-        <v>143.5</v>
+        <v>126</v>
       </c>
       <c r="Z3" t="n">
-        <v>56</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>138</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
@@ -791,14 +815,20 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2017 / Widia Master Catalogue RU</t>
-        </is>
-      </c>
+          <t>2019 / Достижения WIDIA</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TDMX260R1SL32M</t>
+          <t>TDMX250R8SL32M</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -813,12 +843,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>J</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>WID_TopDrillX_K</t>
+          <t>WID_TopDrillX_J</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -827,13 +857,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H4" t="n">
-        <v>26.999</v>
+        <v>25.999</v>
       </c>
       <c r="I4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -852,10 +882,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>41</v>
+        <v>208</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.519</v>
+        <v>8</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -864,7 +894,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>WIDIA_TopDrillX_K</t>
+          <t>WIDIA_TopDrillX_J</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -878,10 +908,10 @@
         <v>32</v>
       </c>
       <c r="X4" t="n">
-        <v>429</v>
+        <v>312</v>
       </c>
       <c r="Y4" t="n">
-        <v>86</v>
+        <v>252</v>
       </c>
       <c r="Z4" t="n">
         <v>60</v>
@@ -897,11 +927,17 @@
           <t>2019 / Достижения WIDIA</t>
         </is>
       </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TDMX250R8SL32M</t>
+          <t>TDM130R3SCF16M</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -911,17 +947,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Top Drill Modular X</t>
+          <t>TOP DRILL M1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>WID_TopDrillX_J</t>
+          <t>WID_TopDrill_W20</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -930,17 +966,17 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>25.999</v>
+        <v>13.49</v>
       </c>
       <c r="I5" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>TDMX..</t>
+          <t>TDM..</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -955,19 +991,19 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>208</v>
+        <v>40.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>3.002</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>ISO_9766:32</t>
+          <t>ISO_9766:16</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>WIDIA_TopDrillX_J</t>
+          <t>WIDIA_TopDrill_W20</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -978,18 +1014,20 @@
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="X5" t="n">
-        <v>312</v>
+        <v>109.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>252</v>
+        <v>61.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA5" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>56</v>
+      </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
@@ -997,14 +1035,20 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2019 / Достижения WIDIA</t>
-        </is>
-      </c>
+          <t>2017 / Widia Master Catalogue RU</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TDM085R3SCF12M</t>
+          <t>TDMX180R3SL25M</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1014,17 +1058,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TOP DRILL M1</t>
+          <t>Top Drill Modular X</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>WID_TopDrill_W11</t>
+          <t>WID_TopDrillX_C</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1033,17 +1077,17 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>8.5</v>
+        <v>18</v>
       </c>
       <c r="H6" t="n">
-        <v>8.99</v>
+        <v>18.999</v>
       </c>
       <c r="I6" t="n">
-        <v>8.5</v>
+        <v>18</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>TDM..</t>
+          <t>TDMX..</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -1058,19 +1102,19 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.003</v>
+        <v>3</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>ISO_9766:12</t>
+          <t>ISO_9766:25</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>WIDIA_TopDrill_W11</t>
+          <t>WIDIA_TopDrillX_C</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -1081,20 +1125,18 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="X6" t="n">
-        <v>87.5</v>
+        <v>146</v>
       </c>
       <c r="Y6" t="n">
-        <v>42.5</v>
+        <v>90</v>
       </c>
       <c r="Z6" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>37</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="n">
@@ -1102,9 +1144,15 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2017 / Widia Master Catalogue RU</t>
-        </is>
-      </c>
+          <t>2019 / Достижения WIDIA</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
